--- a/docs/examples/jordan-lee-demo/expected-outputs/rankings.xlsx
+++ b/docs/examples/jordan-lee-demo/expected-outputs/rankings.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Rankings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Rankings'!$A$1:$Y$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Rankings'!$A$1:$W$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +20,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -44,8 +62,32 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -60,26 +102,68 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+        <bgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00A9D08E"/>
         <bgColor rgb="00A9D08E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4A6A6"/>
         <bgColor rgb="00F4A6A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000000FF"/>
+        <bgColor rgb="000000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FFFF"/>
+        <bgColor rgb="0000FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B3F00"/>
+        <bgColor rgb="007B3F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,40 +193,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -292,7 +398,7 @@
     <author>JAIL</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Prep quarantined 1 thin/failed post(s); they were NOT ranked. See '0 - Prep Report/'.</t>
       </text>
@@ -590,50 +696,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="44" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="48" customWidth="1" min="22" max="22"/>
-    <col width="48" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Date? [You Fill In]</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Status?</t>
+          <t>Status? [You Change]</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -648,102 +752,92 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Location?</t>
+          <t>Working Location</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Comp Range</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Final Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Have Intro? [You Add]</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Your Notes? [You Add]</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decline/Down Date? [You Add]</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Desire Score</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Market Perception Score</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Company Style Score</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Practicality Score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Mission Fit Notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Scope Fit Notes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Top Reasons Notes</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Top Concerns</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Lane Fit</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Location Fit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Comp Range</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Comp Fit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Have Intro?</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Decline/Down Date?</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>lane</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Lane Fit</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>desire_score</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>market_perception_score</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>company_style_score</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>practicality_score</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>final_score</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mission_fit_notes</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>scope_fit_notes</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>top_reasons</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>top_concerns</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>job_file</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ClaudeStatus</t>
+          <t>Job File</t>
         </is>
       </c>
     </row>
@@ -759,94 +853,88 @@
           <t>AI Product Marketing</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Thornbury</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Senior Product Marketing Manager, AI Workflows</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>215-245</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>Meets/above target</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>AI Product Marketing</t>
-        </is>
-      </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="L2" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>AI-native workflow automation with explicit "keep claims honest" culture — directly matches Jordan's values and domain pull</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Positioning, launch GTM, competitive, win-loss research, lifecycle partnership — all core Jordan strengths; no ML-builder or people-management exposure</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>AI-native workflow automation platform squarely in top-priority lane; comp $215K–$245K meets and exceeds target; remote with NYC hybrid optional is preferred setup; "honest AI claims" framing mirrors Jordan's values; strong PMM culture and customer-research mandate; all core PMM duties map directly to Jordan's strengths</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Fictional demo posting — real company/role details unverified; Series B stage means some resource/process ambiguity possible; no information on team size or reporting structure</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>AI Product Marketing (high) · +GTM Strategy</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>AI-native workflow automation with explicit "keep claims honest" culture — directly matches Jordan's values and domain pull</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Positioning, launch GTM, competitive, win-loss research, lifecycle partnership — all core Jordan strengths; no ML-builder or people-management exposure</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>AI-native workflow automation platform squarely in top-priority lane; comp $215K–$245K meets and exceeds target; remote with NYC hybrid optional is preferred setup; "honest AI claims" framing mirrors Jordan's values; strong PMM culture and customer-research mandate; all core PMM duties map directly to Jordan's strengths</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>Fictional demo posting — real company/role details unverified; Series B stage means some resource/process ambiguity possible; no information on team size or reporting structure</t>
-        </is>
-      </c>
-      <c r="X2" s="5" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>Meets/above target</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>thornbury__senior-product-marketing-manager-ai-workflows.txt</t>
         </is>
       </c>
-      <c r="Y2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Apply Eventually: Backup Lane</t>
         </is>
@@ -856,288 +944,328 @@
           <t>AI Product Marketing</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Flintlock</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Principal Product Marketing Manager, Developer AI Platform</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>IRL San Francisco - 5 days</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Other onsite</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>235-275</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>Meets/above target</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>AI Product Marketing</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="L3" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>AI developer tooling is a high-pull domain; infrastructure/platform niche is adjacent but slightly outside Jordan's workflow/productivity SaaS sweet spot</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Positioning, launches, competitive, and technical-buyer enablement match Jordan's strengths; "mentor PMMs" is a light ask Jordan can cover; no ML-building or P&amp;L ownership required</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Comp well above floor and target ($235K–$275K base); AI-native developer tooling aligns with Lane 1; positioning+GTM+competitive scope is a direct match; Principal-level seniority fits Jordan's ~8-year IC trajectory</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Hard dealbreaker — fully onsite San Francisco 5 days/week, relocation explicitly required; developer infrastructure niche is a narrower technical domain than Jordan's workflow/productivity background; mentoring expectation could shade toward light management</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>AI Product Marketing (high) · +GTM Strategy</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>AI developer tooling is a high-pull domain; infrastructure/platform niche is adjacent but slightly outside Jordan's workflow/productivity SaaS sweet spot</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Positioning, launches, competitive, and technical-buyer enablement match Jordan's strengths; "mentor PMMs" is a light ask Jordan can cover; no ML-building or P&amp;L ownership required</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Comp well above floor and target ($235K–$275K base); AI-native developer tooling aligns with Lane 1; positioning+GTM+competitive scope is a direct match; Principal-level seniority fits Jordan's ~8-year IC trajectory</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>Hard dealbreaker — fully onsite San Francisco 5 days/week, relocation explicitly required; developer infrastructure niche is a narrower technical domain than Jordan's workflow/productivity background; mentoring expectation could shade toward light management</t>
-        </is>
-      </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Other onsite</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Meets/above target</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>flintlock__principal-product-marketing-manager-developer-platform.txt</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Apply Eventually: Backup Lane</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>AI Product Marketing</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>GTM Strategy</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Lanternleaf Learning</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>GTM Lead, AI Adoption (Education)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
           <t>150-165</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Below floor</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>AI Product Marketing</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>AI Product Marketing (high) · +GTM Strategy</t>
-        </is>
+      <c r="L4" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="R4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="S4" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>AI tools for under-resourced schools — genuine public-interest mission, a named carve-out in Lane 1</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Role scope (GTM, positioning, launches, light customer research) is a direct match; 5+ year bar leaves Jordan overqualified</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>genuine AI-for-education mission hits Lane 1 carve-out; full GTM ownership and positioning for non-technical buyers aligns exactly with Jordan's strengths; remote-first removes location friction; high-ownership IC role suits leading-without-authority style</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>$150K–$165K base is $15K–$30K below Jordan's hard floor and ~$50K–$65K below target — openly acknowledged as nonprofit discount; no upside signals (equity, bonus) visible to offset; Jordan likely overqualified at 5+ year bar; nonprofit/scrappy resource constraints may limit scope over time</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>GTM Strategy (high) · +AI Product Marketing</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>Below floor</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>lanternleaf-learning__gtm-lead-ai-adoption-education.txt</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>AI Product Marketing</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Apply Eventually: Or Skip It</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Product Strategy / AI Research</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Lyceum AI</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Product Strategy Lead, AI Research Platform</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>IRL NYC - 2 days</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Home hybrid</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>205-245</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Meets/above target</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Outside lanes</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="L5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>AI-native ML tooling company is in Jordan's pull zone, but the product is aimed at ML researchers, not the GTM/workflow buyer Jordan knows</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Role requires owning the product roadmap and ML technical tradeoffs — both are explicit gaps in Jordan's profile and potential dealbreakers</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>comp clears target at $205K–$245K base; NYC hybrid 2 days or fully remote — both preferred arrangements; AI-native company stage and direct culture would suit Jordan's working style</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>core job is PM/product strategy ownership, not PMM — motion mismatch; requires deep ML technical foundation Jordan does not have; roadmap ownership is an explicit profile dealbreaker; recruiter would likely filter Jordan out at resume review; no PMM function or positioning/messaging work described</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>Outside lanes (high)</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>AI-native ML tooling company is in Jordan's pull zone, but the product is aimed at ML researchers, not the GTM/workflow buyer Jordan knows</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>Role requires owning the product roadmap and ML technical tradeoffs — both are explicit gaps in Jordan's profile and potential dealbreakers</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>comp clears target at $205K–$245K base; NYC hybrid 2 days or fully remote — both preferred arrangements; AI-native company stage and direct culture would suit Jordan's working style</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>core job is PM/product strategy ownership, not PMM — motion mismatch; requires deep ML technical foundation Jordan does not have; roadmap ownership is an explicit profile dealbreaker; recruiter would likely filter Jordan out at resume review; no PMM function or positioning/messaging work described</t>
-        </is>
-      </c>
-      <c r="X5" s="5" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>Home hybrid</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>Meets/above target</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>lyceum-ai__product-strategy-lead-ai-research-platform.txt</t>
         </is>
       </c>
-      <c r="Y5" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Section colors  (optional — after sorting by Status, copy a bar in above a group; do NOT paste these into your own tracker's data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>**Currently In Talks**</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Applied: Awaiting Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Apply ASAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Apply Eventually</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Closed / Not Moving Forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Interviewed, Rejected</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y5"/>
-  <conditionalFormatting sqref="O2:O5">
+  <autoFilter ref="A1:W5"/>
+  <mergeCells count="7">
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>85</formula>
     </cfRule>
@@ -1169,7 +1297,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>85</formula>
     </cfRule>
@@ -1201,7 +1329,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>85</formula>
     </cfRule>
@@ -1233,7 +1361,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>85</formula>
     </cfRule>
@@ -1265,7 +1393,7 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S5">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="cellIs" priority="33" operator="greaterThanOrEqual" dxfId="1" stopIfTrue="1">
       <formula>80</formula>
     </cfRule>
@@ -1281,6 +1409,11 @@
       <formula>60</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"**Currently In Talks**,Applied: Awaiting Response,Apply Again??,Apply ASAP: High Prio,Apply Eventually: Apply If Time,Apply Eventually: Backup Lane,Apply Eventually: On Ice (Applied to Another Position at this Company),"&amp;"Apply Eventually: Or Skip It,Declined (Applied, Rejected),Down (Applied, No Response),Down: Closed Before Applying,Interviewed: Rejected"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -1290,4 +1423,165 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>How to use this tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>This spreadsheet is two things at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>A ranking report (AI-scored) AND your living job-search tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Where to start</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Rows are ordered best-fit first by Final Score. Columns whose header ends in "?" are YOURS to fill in (Applied Date, Status, Have Intro, Your Notes, Decline/Down Date).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>"Status? [You Change]" starts from the AI's Final Score:  &gt;=80 Apply ASAP  ·  70-79 Apply If Time  ·  60-69 Backup Lane  ·  &lt;60 Or Skip It.  Pick a new value from the dropdown as each application progresses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>"On Ice" means you already applied to a different role at that company — don't double-apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Grouping &amp; sorting</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>To group by stage, sort by the Status column (use the header filter button, or Data &gt; Sort). The job rows have no merged cells, so sorting works cleanly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Below the jobs is a legend of section colors. If you like visual breaks between groups, copy a bar in above a group after sorting — optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Pasting jobs into your own tracker? Copy only the job rows, NOT the legend bars, so you don't end up with duplicate dividers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Colors &amp; the dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Status / Lane / Location Fit / Comp Fit cells are color-coded. In Google Sheets you can layer the native rounded "chip" dropdown on top if you prefer that look (that is a Sheets feature, not part of the file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>AI detail columns (to the right)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Everything from "Desire Score" rightward is AI-generated.  "Lane" = what the job actually is;  "Lane Fit" = how that maps to your target lanes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>CSV companion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>A matching .csv has the same columns + job rows (no colors, dropdown, legend, or tabs).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>